--- a/experiments/results/resnet34/CIFAR-10/DICE/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/DICE/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1058,6 +1058,104 @@
       <c r="O14" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>99.81</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>96.81</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=50,ash_p=None,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=0.05,type=avg</t>
         </is>
       </c>
     </row>
